--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 11:15</t>
+    <t xml:space="preserve">2026-09-09 22:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:15</t>
+    <t xml:space="preserve">2026-09-17 13:43</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -955,34 +955,34 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="n">
-        <v>15.05</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B3" s="2" t="n">
-        <v>18.91</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B4" s="2" t="n">
-        <v>18.07</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B5" s="2" t="n">
-        <v>14</v>
+        <v>18.07</v>
       </c>
     </row>
   </sheetData>
@@ -1015,134 +1015,134 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>18.43</v>
+        <v>15.11</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>17.71</v>
+        <v>14.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>15.05</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>20.73</v>
+        <v>18.43</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>19.84</v>
+        <v>17.71</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>18.91</v>
+        <v>15.05</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>19.62</v>
+        <v>20.73</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>18.88</v>
+        <v>19.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>18.07</v>
+        <v>18.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>15.11</v>
+        <v>19.62</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>32</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>14.34</v>
+        <v>18.88</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>28</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>14</v>
+        <v>18.07</v>
       </c>
     </row>
     <row r="14">

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
@@ -74,7 +74,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 13:43</t>
+    <t xml:space="preserve">2026-09-25 21:38</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -527,10 +527,10 @@
         <v>17.11</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>-0.2</v>
+        <v>-0.21</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-1.17</v>
+        <v>-1.22</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>5</v>
@@ -576,7 +576,7 @@
         <v>-0.34</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-2.37</v>
+        <v>-2.39</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>5</v>
@@ -619,10 +619,10 @@
         <v>16.57</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-2.91</v>
+        <v>-2.9</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-17.56</v>
+        <v>-17.53</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>4</v>
@@ -645,7 +645,7 @@
         <v>-2.66</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-15.02</v>
+        <v>-15</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>4</v>
@@ -665,10 +665,10 @@
         <v>19.72</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-2.54</v>
+        <v>-2.5</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>3</v>
@@ -737,7 +737,7 @@
         <v>-0.55</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-2.55</v>
+        <v>-2.54</v>
       </c>
       <c r="G11" s="2" t="n">
         <v>2</v>
@@ -757,10 +757,10 @@
         <v>16.95</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>-1</v>
+        <v>-0.99</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-5.9</v>
+        <v>-5.86</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>2</v>
@@ -783,7 +783,7 @@
         <v>-0.81</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-4.29</v>
+        <v>-4.28</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>2</v>
@@ -803,10 +803,10 @@
         <v>21.62</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>-0.62</v>
+        <v>-0.61</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-2.87</v>
+        <v>-2.84</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>1</v>
@@ -826,10 +826,10 @@
         <v>18.47</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-1.16</v>
+        <v>-1.17</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-6.28</v>
+        <v>-6.32</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>1</v>
@@ -852,7 +852,7 @@
         <v>-0.93</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-4.69</v>
+        <v>-4.67</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>1</v>

--- a/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
+++ b/output/laminas_provinciales/prov_i_peringr_median_a_2024_maule.xlsx
@@ -55,7 +55,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-28 21:40</t>
+    <t xml:space="preserve">2026-10-05 07:08</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
